--- a/04_output/P02/M02_Profiling_Nama_NIM.xlsx
+++ b/04_output/P02/M02_Profiling_Nama_NIM.xlsx
@@ -7,13 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M02_Profiling" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temuan_FactSales" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profiling_Audit" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Key_Findings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'M02_Profiling'!$A$4:$H$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Temuan_FactSales'!$A$1:$C$6</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,15 +30,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00123B5D"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <color rgb="0064748B"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -52,7 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00123B5D"/>
+        <fgColor rgb="0017365D"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,21 +54,15 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00D7DEE8"/>
+        <color rgb="00D9E1F2"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -450,278 +432,257 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18.8" customWidth="1" min="1" max="1"/>
+    <col width="16.7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="10.4" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>M02 - Benchmark Profiling</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
+          <t>Query</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kolom profil</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Empty</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Distinct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Unique</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Temuan / Interpretasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Angka acuan dari panduan. Verifikasi ulang pada Power Query dengan profiling based on entire dataset sebelum mengklaim sebagai hasil observasi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Query</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Kolom Profil</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Empty</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Distinct</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Unique</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Temuan</t>
+          <t>Fact_Sales_Raw</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Transaction_ID</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>15734</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>15712</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>15690</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>ID berulang; indikasi duplikasi. Customer_ID 4 empty; Satisfaction_Score 282 empty; Branch_ID 7 distinct; Channel 6 distinct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Dim_Product_Raw</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Product_ID</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Key produk konsisten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Dim_Customer_Raw</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Customer_ID</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Key customer konsisten pada dimensi.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Fact_Sales_Raw</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Transaction_ID</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>15734</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>15712</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>15690</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>ID berulang; indikasi duplikasi, belum dibersihkan pada P02</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Dim_Branch</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Branch_ID</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Master cabang B001-B006.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Dim_Product_Raw</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Product_ID</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>Key produk unik</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Fact_Target</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Branch_ID</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Normal untuk grain bulan x cabang; Branch_ID berulang.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Dim_Customer_Raw</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Customer_ID</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Key pelanggan unik</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Dim_Branch</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Fact_Operations</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Branch_ID</t>
         </is>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C7" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>Master cabang B001-B006</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Fact_Target</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Branch_ID</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>192</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Normal: branch berulang per bulan</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Fact_Operations</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Branch_ID</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>192</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Normal: branch berulang per bulan</t>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Normal untuk grain bulan x cabang; Branch_ID berulang.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H10"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -729,112 +690,109 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Temuan benchmark</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Interpretasi awal</t>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Temuan</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Interpretasi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="n">
+      <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Customer_ID empty = 4</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Missing identifier; dokumentasikan, jangan otomatis diisi.</t>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Customer_ID pada Fact_Sales_Raw: 4 empty</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Missing identifier transaksi perlu didokumentasikan; jangan diisi tanpa aturan.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Satisfaction_Score empty = 282</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Null bukan skor 0; pertahankan sampai ada aturan bisnis.</t>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Satisfaction_Score: 282 empty</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Null berarti respons tidak tersedia; bukan skor 0.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Branch_ID distinct = 7 vs Dim_Branch = 6</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Potensi orphan key; P04 mengaudit B099.</t>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Branch_ID sales: 7 distinct vs Dim_Branch: 6</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Potensi orphan key; diverifikasi di P04 sebagai B099.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Channel distinct = 6 vs 3 kategori bisnis</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Case/spasi perlu standardisasi pada P03.</t>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Channel: 6 distinct vs 3 kanal bisnis</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Butuh Trim/Clean dan mapping eksplisit.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Transaction_ID distinct 15.712 vs 15.734 rows</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>22 baris tambahan terkait ID duplikat; P03 de-dup berdasarkan Transaction_ID.</t>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Transaction_ID: 15.712 distinct dari 15.734 rows</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>22 baris tambahan duplikat ID; dibersihkan di P03.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C6"/>
-  <printOptions horizontalCentered="0"/>
-  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>